--- a/apps/web/public/docs/Modelo_Cuenta_Resultados_Marketplace_5_anos.xlsx
+++ b/apps/web/public/docs/Modelo_Cuenta_Resultados_Marketplace_5_anos.xlsx
@@ -2069,7 +2069,7 @@
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>17% comisión sobre GMV.</t>
+          <t>17% comisión sobre GMV (mín. 4 €/pedido en operativa).</t>
         </is>
       </c>
     </row>
@@ -2088,69 +2088,86 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>3 PyG</t>
+          <t>RETA</t>
         </is>
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>Conservador = referencia. Realista/Optimista = sensibilidad mensual completa.</t>
+          <t>Cuota neta orientativa Socio 2 incluida en Personal/RETA.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Compras</t>
+          <t>Envío</t>
         </is>
       </c>
       <c r="B6" s="34" t="inlineStr">
         <is>
-          <t>0 € — sin reventa de stock.</t>
+          <t>Tarifa plana ~6,50 € siempre al cliente; S.L. no absorbe portes.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>IS/IVA</t>
+          <t>3 PyG</t>
         </is>
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>IS orientativo; IVA fuera de PyG.</t>
+          <t>Conservador = Plan Viabilidad §5. Realista/Optimista = sensibilidad.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Subvenciones</t>
+          <t>Compras</t>
         </is>
       </c>
       <c r="B8" s="34" t="inlineStr">
         <is>
-          <t>No incluidas como ingreso de explotación.</t>
+          <t>0 € — sin reventa de stock.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>IS/IVA</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>IS orientativo; IVA fuera de PyG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Subvenciones</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>No incluidas como ingreso de explotación (entran en caja al cobro).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Dashboard</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>Abrir hoja 00_KPI_Dashboard: gráficos dinámicos desde KPI_Datos / PyG.</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="34" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="34" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="34" t="n"/>
@@ -2484,7 +2501,7 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>10059</v>
+        <v>10018</v>
       </c>
     </row>
     <row r="12">
@@ -2499,7 +2516,7 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -2537,7 +2554,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>16000</v>
+        <v>14000</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>28000</v>
@@ -2547,11 +2564,11 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Aportacion socios (74% ayuda)</t>
+          <t>Aportacion socios (Plan)</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>10400</v>
+        <v>17800</v>
       </c>
     </row>
     <row r="15">
@@ -2559,7 +2576,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>55000</v>
+        <v>48000</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>95000</v>
@@ -2573,7 +2590,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>90000</v>
+        <v>75000</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>150000</v>
@@ -2587,7 +2604,7 @@
         <v>4</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>120000</v>
+        <v>100000</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>200000</v>
@@ -2601,7 +2618,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>145000</v>
+        <v>125000</v>
       </c>
       <c r="C18" s="5" t="n">
         <v>250000</v>
@@ -2644,13 +2661,13 @@
         <v>1</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>-4312</v>
+        <v>-4718</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>-4198</v>
+        <v>-2698</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>-4180</v>
+        <v>-2680</v>
       </c>
     </row>
     <row r="24">
@@ -2658,13 +2675,13 @@
         <v>2</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>-5779</v>
+        <v>-7872</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>-1715</v>
+        <v>1092</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>972</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="25">
@@ -2672,13 +2689,13 @@
         <v>3</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>-1734</v>
+        <v>-4743</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>4055</v>
+        <v>6605</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>7840</v>
+        <v>10390</v>
       </c>
     </row>
     <row r="26">
@@ -2686,13 +2703,13 @@
         <v>4</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>2020</v>
+        <v>-1432</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>9316</v>
+        <v>11866</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>15422</v>
+        <v>17972</v>
       </c>
     </row>
     <row r="27">
@@ -2700,13 +2717,13 @@
         <v>5</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>4956</v>
+        <v>2179</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>14578</v>
+        <v>17128</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>23004</v>
+        <v>25554</v>
       </c>
     </row>
     <row r="30">
@@ -2946,7 +2963,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personal/RETA</t>
         </is>
       </c>
       <c r="B49" s="5">
@@ -3135,7 +3152,7 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personal/RETA</t>
         </is>
       </c>
       <c r="G2" s="38" t="inlineStr">
@@ -3663,7 +3680,7 @@
         <v>28</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P9" s="5" t="n">
         <v>12</v>
@@ -3731,7 +3748,7 @@
         <v>28</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P10" s="5" t="n">
         <v>12</v>
@@ -3799,7 +3816,7 @@
         <v>28</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P11" s="5" t="n">
         <v>12</v>
@@ -3867,7 +3884,7 @@
         <v>28</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P12" s="5" t="n">
         <v>12</v>
@@ -3935,7 +3952,7 @@
         <v>28</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P13" s="5" t="n">
         <v>12</v>
@@ -4003,7 +4020,7 @@
         <v>28</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P14" s="5" t="n">
         <v>12</v>
@@ -4071,7 +4088,7 @@
         <v>28</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P15" s="5" t="n">
         <v>12</v>
@@ -4139,7 +4156,7 @@
         <v>28</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P16" s="5" t="n">
         <v>12</v>
@@ -4207,7 +4224,7 @@
         <v>28</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P17" s="5" t="n">
         <v>12</v>
@@ -4275,7 +4292,7 @@
         <v>28</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P18" s="5" t="n">
         <v>12</v>
@@ -4343,7 +4360,7 @@
         <v>28</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P19" s="5" t="n">
         <v>12</v>
@@ -4411,7 +4428,7 @@
         <v>28</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P20" s="5" t="n">
         <v>12</v>
@@ -4479,7 +4496,7 @@
         <v>28</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P21" s="5" t="n">
         <v>12</v>
@@ -4547,7 +4564,7 @@
         <v>28</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P22" s="5" t="n">
         <v>12</v>
@@ -4615,7 +4632,7 @@
         <v>28</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P23" s="5" t="n">
         <v>12</v>
@@ -4683,7 +4700,7 @@
         <v>28</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P24" s="5" t="n">
         <v>12</v>
@@ -4751,7 +4768,7 @@
         <v>28</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P25" s="5" t="n">
         <v>12</v>
@@ -4819,7 +4836,7 @@
         <v>28</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P26" s="5" t="n">
         <v>12</v>
@@ -4887,7 +4904,7 @@
         <v>28</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P27" s="5" t="n">
         <v>12</v>
@@ -4955,7 +4972,7 @@
         <v>28</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P28" s="5" t="n">
         <v>12</v>
@@ -5023,7 +5040,7 @@
         <v>28</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P29" s="5" t="n">
         <v>12</v>
@@ -5091,7 +5108,7 @@
         <v>28</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P30" s="5" t="n">
         <v>12</v>
@@ -5159,7 +5176,7 @@
         <v>28</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P31" s="5" t="n">
         <v>12</v>
@@ -5227,7 +5244,7 @@
         <v>28</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P32" s="5" t="n">
         <v>12</v>
@@ -5295,7 +5312,7 @@
         <v>28</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P33" s="5" t="n">
         <v>12</v>
@@ -5363,7 +5380,7 @@
         <v>28</v>
       </c>
       <c r="O34" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P34" s="5" t="n">
         <v>12</v>
@@ -5431,7 +5448,7 @@
         <v>28</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P35" s="5" t="n">
         <v>12</v>
@@ -5499,7 +5516,7 @@
         <v>28</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P36" s="5" t="n">
         <v>12</v>
@@ -5567,7 +5584,7 @@
         <v>28</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P37" s="5" t="n">
         <v>12</v>
@@ -5635,7 +5652,7 @@
         <v>28</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P38" s="5" t="n">
         <v>12</v>
@@ -5703,7 +5720,7 @@
         <v>28</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P39" s="5" t="n">
         <v>12</v>
@@ -5771,7 +5788,7 @@
         <v>28</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P40" s="5" t="n">
         <v>12</v>
@@ -5839,7 +5856,7 @@
         <v>28</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P41" s="5" t="n">
         <v>12</v>
@@ -5907,7 +5924,7 @@
         <v>28</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P42" s="5" t="n">
         <v>12</v>
@@ -5975,7 +5992,7 @@
         <v>28</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P43" s="5" t="n">
         <v>12</v>
@@ -6043,7 +6060,7 @@
         <v>28</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P44" s="5" t="n">
         <v>12</v>
@@ -6111,7 +6128,7 @@
         <v>28</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P45" s="5" t="n">
         <v>12</v>
@@ -6179,7 +6196,7 @@
         <v>28</v>
       </c>
       <c r="O46" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P46" s="5" t="n">
         <v>12</v>
@@ -6247,7 +6264,7 @@
         <v>28</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P47" s="5" t="n">
         <v>12</v>
@@ -6315,7 +6332,7 @@
         <v>28</v>
       </c>
       <c r="O48" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P48" s="5" t="n">
         <v>12</v>
@@ -6383,7 +6400,7 @@
         <v>28</v>
       </c>
       <c r="O49" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P49" s="5" t="n">
         <v>12</v>
@@ -6451,7 +6468,7 @@
         <v>28</v>
       </c>
       <c r="O50" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P50" s="5" t="n">
         <v>12</v>
@@ -6519,7 +6536,7 @@
         <v>28</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P51" s="5" t="n">
         <v>12</v>
@@ -6587,7 +6604,7 @@
         <v>28</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P52" s="5" t="n">
         <v>12</v>
@@ -6655,7 +6672,7 @@
         <v>28</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P53" s="5" t="n">
         <v>12</v>
@@ -6723,7 +6740,7 @@
         <v>28</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P54" s="5" t="n">
         <v>12</v>
@@ -6791,7 +6808,7 @@
         <v>28</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P55" s="5" t="n">
         <v>12</v>
@@ -6859,7 +6876,7 @@
         <v>28</v>
       </c>
       <c r="O56" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P56" s="5" t="n">
         <v>12</v>
@@ -6927,7 +6944,7 @@
         <v>28</v>
       </c>
       <c r="O57" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P57" s="5" t="n">
         <v>12</v>
@@ -6995,7 +7012,7 @@
         <v>28</v>
       </c>
       <c r="O58" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P58" s="5" t="n">
         <v>12</v>
@@ -7063,7 +7080,7 @@
         <v>28</v>
       </c>
       <c r="O59" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P59" s="5" t="n">
         <v>12</v>
@@ -7131,7 +7148,7 @@
         <v>28</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P60" s="5" t="n">
         <v>12</v>
@@ -7199,7 +7216,7 @@
         <v>28</v>
       </c>
       <c r="O61" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P61" s="5" t="n">
         <v>12</v>
@@ -7267,7 +7284,7 @@
         <v>28</v>
       </c>
       <c r="O62" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P62" s="5" t="n">
         <v>12</v>
@@ -7363,7 +7380,7 @@
       </c>
       <c r="F2" s="38" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personal/RETA</t>
         </is>
       </c>
       <c r="G2" s="38" t="inlineStr">
@@ -7891,7 +7908,7 @@
         <v>35</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P9" s="5" t="n">
         <v>18</v>
@@ -7959,7 +7976,7 @@
         <v>35</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P10" s="5" t="n">
         <v>18</v>
@@ -8027,7 +8044,7 @@
         <v>35</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P11" s="5" t="n">
         <v>18</v>
@@ -8095,7 +8112,7 @@
         <v>35</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P12" s="5" t="n">
         <v>18</v>
@@ -8163,7 +8180,7 @@
         <v>35</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P13" s="5" t="n">
         <v>18</v>
@@ -8231,7 +8248,7 @@
         <v>35</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P14" s="5" t="n">
         <v>18</v>
@@ -8299,7 +8316,7 @@
         <v>35</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P15" s="5" t="n">
         <v>18</v>
@@ -8367,7 +8384,7 @@
         <v>35</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P16" s="5" t="n">
         <v>18</v>
@@ -8435,7 +8452,7 @@
         <v>35</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P17" s="5" t="n">
         <v>18</v>
@@ -8503,7 +8520,7 @@
         <v>35</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P18" s="5" t="n">
         <v>18</v>
@@ -8571,7 +8588,7 @@
         <v>35</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P19" s="5" t="n">
         <v>18</v>
@@ -8639,7 +8656,7 @@
         <v>35</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P20" s="5" t="n">
         <v>18</v>
@@ -8707,7 +8724,7 @@
         <v>35</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P21" s="5" t="n">
         <v>18</v>
@@ -8775,7 +8792,7 @@
         <v>35</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P22" s="5" t="n">
         <v>18</v>
@@ -8843,7 +8860,7 @@
         <v>35</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P23" s="5" t="n">
         <v>18</v>
@@ -8911,7 +8928,7 @@
         <v>35</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P24" s="5" t="n">
         <v>18</v>
@@ -8979,7 +8996,7 @@
         <v>35</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P25" s="5" t="n">
         <v>18</v>
@@ -9047,7 +9064,7 @@
         <v>35</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P26" s="5" t="n">
         <v>18</v>
@@ -9115,7 +9132,7 @@
         <v>35</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P27" s="5" t="n">
         <v>18</v>
@@ -9183,7 +9200,7 @@
         <v>35</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P28" s="5" t="n">
         <v>18</v>
@@ -9251,7 +9268,7 @@
         <v>35</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P29" s="5" t="n">
         <v>18</v>
@@ -9319,7 +9336,7 @@
         <v>35</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P30" s="5" t="n">
         <v>18</v>
@@ -9387,7 +9404,7 @@
         <v>35</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P31" s="5" t="n">
         <v>18</v>
@@ -9455,7 +9472,7 @@
         <v>35</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P32" s="5" t="n">
         <v>18</v>
@@ -9523,7 +9540,7 @@
         <v>35</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P33" s="5" t="n">
         <v>18</v>
@@ -9591,7 +9608,7 @@
         <v>35</v>
       </c>
       <c r="O34" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P34" s="5" t="n">
         <v>18</v>
@@ -9659,7 +9676,7 @@
         <v>35</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P35" s="5" t="n">
         <v>18</v>
@@ -9727,7 +9744,7 @@
         <v>35</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P36" s="5" t="n">
         <v>18</v>
@@ -9795,7 +9812,7 @@
         <v>35</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P37" s="5" t="n">
         <v>18</v>
@@ -9863,7 +9880,7 @@
         <v>35</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P38" s="5" t="n">
         <v>18</v>
@@ -9931,7 +9948,7 @@
         <v>35</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P39" s="5" t="n">
         <v>18</v>
@@ -9999,7 +10016,7 @@
         <v>35</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P40" s="5" t="n">
         <v>18</v>
@@ -10067,7 +10084,7 @@
         <v>35</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P41" s="5" t="n">
         <v>18</v>
@@ -10135,7 +10152,7 @@
         <v>35</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P42" s="5" t="n">
         <v>18</v>
@@ -10203,7 +10220,7 @@
         <v>35</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P43" s="5" t="n">
         <v>18</v>
@@ -10271,7 +10288,7 @@
         <v>35</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P44" s="5" t="n">
         <v>18</v>
@@ -10339,7 +10356,7 @@
         <v>35</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P45" s="5" t="n">
         <v>18</v>
@@ -10407,7 +10424,7 @@
         <v>35</v>
       </c>
       <c r="O46" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P46" s="5" t="n">
         <v>18</v>
@@ -10475,7 +10492,7 @@
         <v>35</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P47" s="5" t="n">
         <v>18</v>
@@ -10543,7 +10560,7 @@
         <v>35</v>
       </c>
       <c r="O48" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P48" s="5" t="n">
         <v>18</v>
@@ -10611,7 +10628,7 @@
         <v>35</v>
       </c>
       <c r="O49" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P49" s="5" t="n">
         <v>18</v>
@@ -10679,7 +10696,7 @@
         <v>35</v>
       </c>
       <c r="O50" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P50" s="5" t="n">
         <v>18</v>
@@ -10747,7 +10764,7 @@
         <v>35</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P51" s="5" t="n">
         <v>18</v>
@@ -10815,7 +10832,7 @@
         <v>35</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P52" s="5" t="n">
         <v>18</v>
@@ -10883,7 +10900,7 @@
         <v>35</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P53" s="5" t="n">
         <v>18</v>
@@ -10951,7 +10968,7 @@
         <v>35</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P54" s="5" t="n">
         <v>18</v>
@@ -11019,7 +11036,7 @@
         <v>35</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P55" s="5" t="n">
         <v>18</v>
@@ -11087,7 +11104,7 @@
         <v>35</v>
       </c>
       <c r="O56" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P56" s="5" t="n">
         <v>18</v>
@@ -11155,7 +11172,7 @@
         <v>35</v>
       </c>
       <c r="O57" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P57" s="5" t="n">
         <v>18</v>
@@ -11223,7 +11240,7 @@
         <v>35</v>
       </c>
       <c r="O58" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P58" s="5" t="n">
         <v>18</v>
@@ -11291,7 +11308,7 @@
         <v>35</v>
       </c>
       <c r="O59" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P59" s="5" t="n">
         <v>18</v>
@@ -11359,7 +11376,7 @@
         <v>35</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P60" s="5" t="n">
         <v>18</v>
@@ -11427,7 +11444,7 @@
         <v>35</v>
       </c>
       <c r="O61" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P61" s="5" t="n">
         <v>18</v>
@@ -11495,7 +11512,7 @@
         <v>35</v>
       </c>
       <c r="O62" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P62" s="5" t="n">
         <v>18</v>
@@ -11610,7 +11627,7 @@
       </c>
       <c r="F2" s="43" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Personal/RETA</t>
         </is>
       </c>
       <c r="G2" s="43" t="inlineStr">
@@ -11706,34 +11723,34 @@
         <v>0</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="5">
         <f>SUM(E3:P3)</f>
@@ -11774,34 +11791,34 @@
         <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="5">
         <f>SUM(E4:P4)</f>
@@ -11842,34 +11859,34 @@
         <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="5">
         <f>SUM(E5:P5)</f>
@@ -11910,34 +11927,34 @@
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="5">
         <f>SUM(E6:P6)</f>
@@ -11978,34 +11995,34 @@
         <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="5">
         <f>SUM(E7:P7)</f>
@@ -12046,34 +12063,34 @@
         <v>0</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="5">
         <f>SUM(E8:P8)</f>
@@ -12102,46 +12119,46 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3032.52</v>
+        <v>2653.46</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>515.53</v>
+        <v>451.09</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>45.49</v>
+        <v>39.8</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>200</v>
+        <v>333</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L9" s="5" t="n">
         <v>20</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N9" s="5" t="n">
         <v>15</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q9" s="5">
         <f>SUM(E9:P9)</f>
@@ -12170,46 +12187,46 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>4397.16</v>
+        <v>3847.51</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>747.52</v>
+        <v>654.08</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>65.95999999999999</v>
+        <v>57.71</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>200</v>
+        <v>333</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L10" s="5" t="n">
         <v>20</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N10" s="5" t="n">
         <v>15</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q10" s="5">
         <f>SUM(E10:P10)</f>
@@ -12238,46 +12255,46 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2164.38</v>
+        <v>1893.83</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>367.94</v>
+        <v>321.95</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>32.47</v>
+        <v>28.41</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>200</v>
+        <v>333</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L11" s="5" t="n">
         <v>20</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N11" s="5" t="n">
         <v>15</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q11" s="5">
         <f>SUM(E11:P11)</f>
@@ -12306,46 +12323,46 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2400.33</v>
+        <v>2100.28</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>408.06</v>
+        <v>357.05</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>36</v>
+        <v>31.5</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>200</v>
+        <v>333</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>20</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>15</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q12" s="5">
         <f>SUM(E12:P12)</f>
@@ -12374,46 +12391,46 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>2073.91</v>
+        <v>1814.67</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>352.56</v>
+        <v>308.49</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>31.11</v>
+        <v>27.22</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>200</v>
+        <v>333</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L13" s="5" t="n">
         <v>20</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N13" s="5" t="n">
         <v>15</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q13" s="5">
         <f>SUM(E13:P13)</f>
@@ -12442,46 +12459,46 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>1931.7</v>
+        <v>1690.23</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>328.39</v>
+        <v>287.34</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>28.98</v>
+        <v>25.35</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>200</v>
+        <v>333</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>20</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>15</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q14" s="5">
         <f>SUM(E14:P14)</f>
@@ -12510,46 +12527,46 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>2104.88</v>
+        <v>1836.99</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>357.83</v>
+        <v>312.29</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>31.57</v>
+        <v>27.55</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K15" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M15" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L15" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N15" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q15" s="5">
         <f>SUM(E15:P15)</f>
@@ -12578,46 +12595,46 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>2945.46</v>
+        <v>2570.58</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>500.73</v>
+        <v>437</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>44.18</v>
+        <v>38.56</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M16" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L16" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N16" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q16" s="5">
         <f>SUM(E16:P16)</f>
@@ -12646,46 +12663,46 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>4369.62</v>
+        <v>3813.49</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>742.84</v>
+        <v>648.29</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>65.54000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K17" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M17" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L17" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M17" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N17" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q17" s="5">
         <f>SUM(E17:P17)</f>
@@ -12714,46 +12731,46 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>2982.94</v>
+        <v>2603.29</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>507.1</v>
+        <v>442.56</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>44.74</v>
+        <v>39.05</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K18" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M18" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L18" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N18" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q18" s="5">
         <f>SUM(E18:P18)</f>
@@ -12782,46 +12799,46 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>4236.54</v>
+        <v>3697.34</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>720.21</v>
+        <v>628.55</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>63.55</v>
+        <v>55.46</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M19" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L19" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N19" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q19" s="5">
         <f>SUM(E19:P19)</f>
@@ -12850,46 +12867,46 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>4543.24</v>
+        <v>3965.01</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>772.35</v>
+        <v>674.05</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>68.15000000000001</v>
+        <v>59.48</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M20" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L20" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N20" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="5">
         <f>SUM(E20:P20)</f>
@@ -12918,46 +12935,46 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>6409.49</v>
+        <v>5593.74</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1089.61</v>
+        <v>950.9400000000001</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>96.14</v>
+        <v>83.91</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K21" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M21" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L21" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N21" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q21" s="5">
         <f>SUM(E21:P21)</f>
@@ -12986,46 +13003,46 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>9293.76</v>
+        <v>8110.92</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>1579.94</v>
+        <v>1378.86</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>139.41</v>
+        <v>121.66</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K22" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M22" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L22" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N22" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O22" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q22" s="5">
         <f>SUM(E22:P22)</f>
@@ -13054,46 +13071,46 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>4574.6</v>
+        <v>3992.38</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>777.6799999999999</v>
+        <v>678.7</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>68.62</v>
+        <v>59.89</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K23" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M23" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L23" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M23" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N23" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O23" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P23" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q23" s="5">
         <f>SUM(E23:P23)</f>
@@ -13122,46 +13139,46 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>5073.29</v>
+        <v>4427.6</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>862.46</v>
+        <v>752.6900000000001</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>76.09999999999999</v>
+        <v>66.41</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K24" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M24" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L24" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N24" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q24" s="5">
         <f>SUM(E24:P24)</f>
@@ -13190,46 +13207,46 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>4383.39</v>
+        <v>3825.5</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>745.1799999999999</v>
+        <v>650.34</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>65.75</v>
+        <v>57.38</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K25" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M25" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L25" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M25" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N25" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O25" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P25" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q25" s="5">
         <f>SUM(E25:P25)</f>
@@ -13258,46 +13275,46 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>4082.8</v>
+        <v>3563.17</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>694.08</v>
+        <v>605.74</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>61.24</v>
+        <v>53.45</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K26" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M26" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L26" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N26" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q26" s="5">
         <f>SUM(E26:P26)</f>
@@ -13326,46 +13343,46 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>3444.35</v>
+        <v>2870.29</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>585.54</v>
+        <v>487.95</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>51.67</v>
+        <v>43.05</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>300</v>
+        <v>458</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K27" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M27" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L27" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M27" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N27" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O27" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q27" s="5">
         <f>SUM(E27:P27)</f>
@@ -13394,46 +13411,46 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>4819.84</v>
+        <v>4016.53</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>819.37</v>
+        <v>682.8099999999999</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>72.3</v>
+        <v>60.25</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>300</v>
+        <v>458</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K28" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M28" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L28" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N28" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q28" s="5">
         <f>SUM(E28:P28)</f>
@@ -13462,46 +13479,46 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>7150.29</v>
+        <v>5958.57</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1215.55</v>
+        <v>1012.96</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>107.25</v>
+        <v>89.38</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>300</v>
+        <v>458</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K29" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M29" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L29" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M29" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N29" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O29" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P29" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q29" s="5">
         <f>SUM(E29:P29)</f>
@@ -13530,46 +13547,46 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>4881.17</v>
+        <v>4067.64</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>829.8</v>
+        <v>691.5</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>73.22</v>
+        <v>61.01</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>300</v>
+        <v>458</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K30" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M30" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L30" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N30" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q30" s="5">
         <f>SUM(E30:P30)</f>
@@ -13598,46 +13615,46 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>6932.51</v>
+        <v>5777.09</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1178.53</v>
+        <v>982.11</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>103.99</v>
+        <v>86.66</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>300</v>
+        <v>458</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K31" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M31" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L31" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M31" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N31" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O31" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P31" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q31" s="5">
         <f>SUM(E31:P31)</f>
@@ -13666,46 +13683,46 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>7434.4</v>
+        <v>6195.33</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>1263.85</v>
+        <v>1053.21</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>111.52</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>300</v>
+        <v>458</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K32" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M32" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L32" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N32" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O32" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P32" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q32" s="5">
         <f>SUM(E32:P32)</f>
@@ -13734,46 +13751,46 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>10488.26</v>
+        <v>8740.209999999999</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>1783</v>
+        <v>1485.84</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>157.32</v>
+        <v>131.1</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>300</v>
+        <v>458</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M33" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L33" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N33" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O33" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P33" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q33" s="5">
         <f>SUM(E33:P33)</f>
@@ -13802,46 +13819,46 @@
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>15207.97</v>
+        <v>12673.31</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>2585.35</v>
+        <v>2154.46</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>228.12</v>
+        <v>190.1</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>300</v>
+        <v>458</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K34" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M34" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L34" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M34" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N34" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O34" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q34" s="5">
         <f>SUM(E34:P34)</f>
@@ -13870,46 +13887,46 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>7485.71</v>
+        <v>6238.09</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>1272.57</v>
+        <v>1060.48</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>112.29</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>300</v>
+        <v>458</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K35" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M35" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L35" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M35" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N35" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O35" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P35" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q35" s="5">
         <f>SUM(E35:P35)</f>
@@ -13938,46 +13955,46 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>8301.74</v>
+        <v>6918.12</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>1411.3</v>
+        <v>1176.08</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>124.53</v>
+        <v>103.77</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>300</v>
+        <v>458</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K36" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M36" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L36" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N36" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O36" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P36" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q36" s="5">
         <f>SUM(E36:P36)</f>
@@ -14006,46 +14023,46 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>7172.82</v>
+        <v>5977.35</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>1219.38</v>
+        <v>1016.15</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>107.59</v>
+        <v>89.66</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>300</v>
+        <v>458</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K37" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M37" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L37" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M37" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N37" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O37" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P37" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q37" s="5">
         <f>SUM(E37:P37)</f>
@@ -14074,46 +14091,46 @@
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>6680.94</v>
+        <v>5567.45</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>1135.76</v>
+        <v>946.47</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>100.21</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>300</v>
+        <v>458</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K38" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M38" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L38" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M38" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N38" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O38" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q38" s="5">
         <f>SUM(E38:P38)</f>
@@ -14142,46 +14159,46 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>4592.47</v>
+        <v>3827.06</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>780.72</v>
+        <v>650.6</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>68.89</v>
+        <v>57.41</v>
       </c>
       <c r="F39" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="I39" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="G39" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>310</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>175</v>
-      </c>
       <c r="J39" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K39" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M39" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L39" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M39" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N39" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O39" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P39" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q39" s="5">
         <f>SUM(E39:P39)</f>
@@ -14210,46 +14227,46 @@
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>6426.46</v>
+        <v>5355.38</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>1092.5</v>
+        <v>910.41</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>96.40000000000001</v>
+        <v>80.33</v>
       </c>
       <c r="F40" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="I40" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="G40" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>310</v>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>175</v>
-      </c>
       <c r="J40" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K40" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M40" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L40" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N40" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O40" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q40" s="5">
         <f>SUM(E40:P40)</f>
@@ -14278,46 +14295,46 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>9533.719999999999</v>
+        <v>7944.76</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>1620.73</v>
+        <v>1350.61</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>143.01</v>
+        <v>119.17</v>
       </c>
       <c r="F41" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="I41" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="G41" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>310</v>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>175</v>
-      </c>
       <c r="J41" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K41" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M41" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L41" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M41" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N41" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O41" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P41" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q41" s="5">
         <f>SUM(E41:P41)</f>
@@ -14346,46 +14363,46 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>6508.23</v>
+        <v>5423.52</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>1106.4</v>
+        <v>922</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>97.62</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="F42" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="I42" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="G42" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>310</v>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>175</v>
-      </c>
       <c r="J42" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K42" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M42" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L42" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M42" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N42" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P42" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q42" s="5">
         <f>SUM(E42:P42)</f>
@@ -14414,46 +14431,46 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>9243.35</v>
+        <v>7702.79</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>1571.37</v>
+        <v>1309.47</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>138.65</v>
+        <v>115.54</v>
       </c>
       <c r="F43" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="I43" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="G43" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>310</v>
-      </c>
-      <c r="I43" s="5" t="n">
-        <v>175</v>
-      </c>
       <c r="J43" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K43" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M43" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L43" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M43" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N43" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O43" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P43" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q43" s="5">
         <f>SUM(E43:P43)</f>
@@ -14482,46 +14499,46 @@
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>9912.530000000001</v>
+        <v>8260.440000000001</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>1685.13</v>
+        <v>1404.27</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>148.69</v>
+        <v>123.91</v>
       </c>
       <c r="F44" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="I44" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="G44" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H44" s="5" t="n">
-        <v>310</v>
-      </c>
-      <c r="I44" s="5" t="n">
-        <v>175</v>
-      </c>
       <c r="J44" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K44" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M44" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L44" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N44" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q44" s="5">
         <f>SUM(E44:P44)</f>
@@ -14550,46 +14567,46 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>13984.34</v>
+        <v>11653.62</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>2377.34</v>
+        <v>1981.12</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>209.77</v>
+        <v>174.8</v>
       </c>
       <c r="F45" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="I45" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="G45" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H45" s="5" t="n">
-        <v>310</v>
-      </c>
-      <c r="I45" s="5" t="n">
-        <v>175</v>
-      </c>
       <c r="J45" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K45" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M45" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L45" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M45" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N45" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P45" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q45" s="5">
         <f>SUM(E45:P45)</f>
@@ -14618,46 +14635,46 @@
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>20277.29</v>
+        <v>16897.75</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>3447.14</v>
+        <v>2872.62</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>304.16</v>
+        <v>253.47</v>
       </c>
       <c r="F46" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="I46" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="G46" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H46" s="5" t="n">
-        <v>310</v>
-      </c>
-      <c r="I46" s="5" t="n">
-        <v>175</v>
-      </c>
       <c r="J46" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K46" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M46" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L46" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N46" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O46" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P46" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q46" s="5">
         <f>SUM(E46:P46)</f>
@@ -14686,46 +14703,46 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>9980.950000000001</v>
+        <v>8317.459999999999</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>1696.76</v>
+        <v>1413.97</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>149.71</v>
+        <v>124.76</v>
       </c>
       <c r="F47" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="I47" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="G47" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H47" s="5" t="n">
-        <v>310</v>
-      </c>
-      <c r="I47" s="5" t="n">
-        <v>175</v>
-      </c>
       <c r="J47" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K47" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M47" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L47" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M47" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N47" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O47" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P47" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q47" s="5">
         <f>SUM(E47:P47)</f>
@@ -14754,46 +14771,46 @@
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>11068.99</v>
+        <v>9224.16</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>1881.73</v>
+        <v>1568.11</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>166.03</v>
+        <v>138.36</v>
       </c>
       <c r="F48" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="I48" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="G48" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H48" s="5" t="n">
-        <v>310</v>
-      </c>
-      <c r="I48" s="5" t="n">
-        <v>175</v>
-      </c>
       <c r="J48" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K48" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M48" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L48" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M48" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N48" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O48" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P48" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q48" s="5">
         <f>SUM(E48:P48)</f>
@@ -14822,46 +14839,46 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>9563.75</v>
+        <v>7969.8</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>1625.84</v>
+        <v>1354.87</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>143.46</v>
+        <v>119.55</v>
       </c>
       <c r="F49" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="I49" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="G49" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>310</v>
-      </c>
-      <c r="I49" s="5" t="n">
-        <v>175</v>
-      </c>
       <c r="J49" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K49" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M49" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L49" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M49" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N49" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O49" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P49" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q49" s="5">
         <f>SUM(E49:P49)</f>
@@ -14890,46 +14907,46 @@
         </is>
       </c>
       <c r="C50" s="5" t="n">
-        <v>8907.93</v>
+        <v>7423.27</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>1514.35</v>
+        <v>1261.96</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>133.62</v>
+        <v>111.35</v>
       </c>
       <c r="F50" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="I50" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="G50" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H50" s="5" t="n">
-        <v>310</v>
-      </c>
-      <c r="I50" s="5" t="n">
-        <v>175</v>
-      </c>
       <c r="J50" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K50" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M50" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L50" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M50" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N50" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O50" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q50" s="5">
         <f>SUM(E50:P50)</f>
@@ -14958,46 +14975,46 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>5549.24</v>
+        <v>4783.82</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>943.37</v>
+        <v>813.25</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>83.23999999999999</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K51" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M51" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L51" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M51" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N51" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O51" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P51" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q51" s="5">
         <f>SUM(E51:P51)</f>
@@ -15026,46 +15043,46 @@
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>7765.3</v>
+        <v>6694.22</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>1320.1</v>
+        <v>1138.02</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>116.48</v>
+        <v>100.41</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K52" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M52" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L52" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M52" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N52" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q52" s="5">
         <f>SUM(E52:P52)</f>
@@ -15094,46 +15111,46 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>11519.91</v>
+        <v>9930.950000000001</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>1958.38</v>
+        <v>1688.26</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>172.8</v>
+        <v>148.96</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K53" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M53" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L53" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M53" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N53" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O53" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P53" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q53" s="5">
         <f>SUM(E53:P53)</f>
@@ -15162,46 +15179,46 @@
         </is>
       </c>
       <c r="C54" s="5" t="n">
-        <v>7864.11</v>
+        <v>6779.4</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>1336.9</v>
+        <v>1152.5</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>117.96</v>
+        <v>101.69</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K54" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M54" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L54" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N54" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q54" s="5">
         <f>SUM(E54:P54)</f>
@@ -15230,46 +15247,46 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>11169.05</v>
+        <v>9628.49</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>1898.74</v>
+        <v>1636.84</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>167.54</v>
+        <v>144.43</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K55" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M55" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L55" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M55" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N55" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O55" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P55" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q55" s="5">
         <f>SUM(E55:P55)</f>
@@ -15298,46 +15315,46 @@
         </is>
       </c>
       <c r="C56" s="5" t="n">
-        <v>11977.64</v>
+        <v>10325.55</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>2036.2</v>
+        <v>1755.34</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>179.66</v>
+        <v>154.88</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K56" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M56" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L56" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N56" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O56" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q56" s="5">
         <f>SUM(E56:P56)</f>
@@ -15366,46 +15383,46 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>16897.75</v>
+        <v>14567.02</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>2872.62</v>
+        <v>2476.39</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>253.47</v>
+        <v>218.51</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K57" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M57" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L57" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M57" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N57" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O57" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P57" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q57" s="5">
         <f>SUM(E57:P57)</f>
@@ -15434,46 +15451,46 @@
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>24501.73</v>
+        <v>21122.18</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>4165.29</v>
+        <v>3590.77</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>367.53</v>
+        <v>316.83</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K58" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M58" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L58" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M58" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N58" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O58" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P58" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q58" s="5">
         <f>SUM(E58:P58)</f>
@@ -15502,46 +15519,46 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>12060.31</v>
+        <v>10396.82</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>2050.25</v>
+        <v>1767.46</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>180.9</v>
+        <v>155.95</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K59" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M59" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L59" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M59" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N59" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O59" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P59" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q59" s="5">
         <f>SUM(E59:P59)</f>
@@ -15570,46 +15587,46 @@
         </is>
       </c>
       <c r="C60" s="5" t="n">
-        <v>13375.03</v>
+        <v>11530.2</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>2273.76</v>
+        <v>1960.13</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>200.63</v>
+        <v>172.95</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K60" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M60" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L60" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N60" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P60" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q60" s="5">
         <f>SUM(E60:P60)</f>
@@ -15638,46 +15655,46 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>11556.2</v>
+        <v>9962.24</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>1964.55</v>
+        <v>1693.58</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>173.34</v>
+        <v>149.43</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K61" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M61" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L61" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M61" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N61" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O61" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P61" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q61" s="5">
         <f>SUM(E61:P61)</f>
@@ -15706,46 +15723,46 @@
         </is>
       </c>
       <c r="C62" s="5" t="n">
-        <v>10763.74</v>
+        <v>9279.09</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>1829.84</v>
+        <v>1577.45</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>161.46</v>
+        <v>139.19</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K62" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M62" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="L62" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="N62" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="O62" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="P62" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q62" s="5">
         <f>SUM(E62:P62)</f>
@@ -15872,11 +15889,11 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>16000</v>
+        <v>14000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>→ 2,720 € comisión (6 meses venta)</t>
+          <t>→ 2,380 € comisión (6 meses venta)</t>
         </is>
       </c>
     </row>
@@ -15887,11 +15904,11 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>55000</v>
+        <v>48000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>→ 9,350 € comisión</t>
+          <t>→ 8,160 € comisión</t>
         </is>
       </c>
     </row>
@@ -15902,11 +15919,11 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>90000</v>
+        <v>75000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>→ 15,300 € comisión</t>
+          <t>→ 12,750 € comisión</t>
         </is>
       </c>
     </row>
@@ -15932,18 +15949,18 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>30.000/5; en Y1 solo jul–dic</t>
+          <t>Amort. contable ligera; Y1 solo jul–dic</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Inversión referencia</t>
+          <t>Inversión / capital social</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
@@ -15951,7 +15968,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Activo tecnológico / umbral ICECYL</t>
+          <t>Caja arranque 40k (elegible tip. 30k)</t>
         </is>
       </c>
     </row>
@@ -15973,58 +15990,98 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aportacion real socios</t>
+          <t>Aportacion neto socios (Plan)</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>10400</v>
+        <v>17800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>40k elegible - 29,6k subvencion (74%)</t>
+          <t>40k − 22,2k ayuda (74% sobre 30k elegibles)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Compras mercancía</t>
+          <t>Aportacion si elegible 40k</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0</v>
+        <v>10400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Intermediación: sin COGS</t>
+          <t>Hipótesis dossier: 40k − 29,6k</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Compras mercancía</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Intermediación: sin COGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Envío</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>Cliente paga 6,50 €</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>S.L. no absorbe portes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Suavizado Y1</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Amort. y marketing comercial desde lanzamiento; H1 costes mínimos</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="1" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="1" t="n"/>
-    </row>
     <row r="18">
-      <c r="B18" s="3" t="n"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>RETA Socio 2</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Sí (neto orient.)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Incluido en Personal/RETA</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="1" t="n"/>
@@ -16100,16 +16157,16 @@
         <v>5</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1333.33</v>
+        <v>466.67</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>40000</v>
+        <v>14000</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>6000</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="5">
@@ -16117,19 +16174,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5" s="18" t="n">
-        <v>1458.33</v>
+        <v>666.67</v>
       </c>
       <c r="D5" s="17" t="n">
         <v>12</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>140000</v>
+        <v>48000</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>21000</v>
+        <v>8160</v>
       </c>
       <c r="G5" s="17" t="n"/>
     </row>
@@ -16138,19 +16195,19 @@
         <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1666.67</v>
+        <v>781.25</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>220000</v>
+        <v>75000</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>33000</v>
+        <v>12750</v>
       </c>
     </row>
     <row r="7">
@@ -16158,19 +16215,19 @@
         <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1794.87</v>
+        <v>925.9299999999999</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>280000</v>
+        <v>100000</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>42000</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="8">
@@ -16178,19 +16235,19 @@
         <v>5</v>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>2000</v>
+        <v>1041.67</v>
       </c>
       <c r="D8" t="n">
         <v>12</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>360000</v>
+        <v>125000</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>54000</v>
+        <v>21250</v>
       </c>
     </row>
     <row r="9">
@@ -16215,7 +16272,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1710</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="12">
@@ -16225,17 +16282,17 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>10058.82</v>
+        <v>9929.41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Con 11 vendedores → GMV/vend/mes</t>
+          <t>Con 8 vendedores → GMV/vend/mes</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>914.4400000000001</v>
+        <v>1241.18</v>
       </c>
     </row>
     <row r="14">
@@ -16262,21 +16319,21 @@
     <row r="17" ht="45" customHeight="1" s="32">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Aportacion socios (sin subvencion al 74%)</t>
+          <t>Aportacion socios (Plan Viabilidad ≈17,8k)</t>
         </is>
       </c>
       <c r="B17" s="68" t="n">
-        <v>0</v>
+        <v>17800</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Neto acumulado objetivo (5 años)</t>
+          <t>Aportacion si elegible 40k (≈10,4k)</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>40000</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="19">
@@ -16286,11 +16343,11 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>-4849</v>
+        <v>-16586</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>REVISAR</t>
+          <t>Pérdida esperada Y1–Y3; subvención sostiene</t>
         </is>
       </c>
     </row>
@@ -16366,16 +16423,16 @@
         <v>1</v>
       </c>
       <c r="C4" s="47" t="n">
-        <v>16000</v>
+        <v>14000</v>
       </c>
       <c r="D4" s="47" t="n">
-        <v>2720</v>
+        <v>2380</v>
       </c>
       <c r="E4" s="47" t="n">
-        <v>7032</v>
+        <v>7098</v>
       </c>
       <c r="F4" s="47" t="n">
-        <v>-4312</v>
+        <v>-4718</v>
       </c>
     </row>
     <row r="5">
@@ -16388,16 +16445,16 @@
         <v>2</v>
       </c>
       <c r="C5" s="49" t="n">
-        <v>55000</v>
+        <v>48000</v>
       </c>
       <c r="D5" s="49" t="n">
-        <v>9350</v>
+        <v>8160</v>
       </c>
       <c r="E5" s="49" t="n">
-        <v>15129</v>
+        <v>16032</v>
       </c>
       <c r="F5" s="49" t="n">
-        <v>-5779</v>
+        <v>-7872</v>
       </c>
     </row>
     <row r="6">
@@ -16410,16 +16467,16 @@
         <v>3</v>
       </c>
       <c r="C6" s="49" t="n">
-        <v>90000</v>
+        <v>75000</v>
       </c>
       <c r="D6" s="49" t="n">
-        <v>15300</v>
+        <v>12750</v>
       </c>
       <c r="E6" s="49" t="n">
-        <v>17034</v>
+        <v>17493</v>
       </c>
       <c r="F6" s="49" t="n">
-        <v>-1734</v>
+        <v>-4743</v>
       </c>
     </row>
     <row r="7">
@@ -16432,16 +16489,16 @@
         <v>4</v>
       </c>
       <c r="C7" s="49" t="n">
-        <v>120000</v>
+        <v>100000</v>
       </c>
       <c r="D7" s="49" t="n">
-        <v>20400</v>
+        <v>17000</v>
       </c>
       <c r="E7" s="49" t="n">
-        <v>18024</v>
+        <v>18432</v>
       </c>
       <c r="F7" s="49" t="n">
-        <v>2376</v>
+        <v>-1432</v>
       </c>
     </row>
     <row r="8">
@@ -16454,16 +16511,16 @@
         <v>5</v>
       </c>
       <c r="C8" s="49" t="n">
-        <v>145000</v>
+        <v>125000</v>
       </c>
       <c r="D8" s="49" t="n">
-        <v>24650</v>
+        <v>21250</v>
       </c>
       <c r="E8" s="49" t="n">
-        <v>18819</v>
+        <v>18687</v>
       </c>
       <c r="F8" s="49" t="n">
-        <v>5831</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="9">
@@ -16482,10 +16539,10 @@
         <v>4760</v>
       </c>
       <c r="E9" s="51" t="n">
-        <v>8958</v>
+        <v>7458</v>
       </c>
       <c r="F9" s="51" t="n">
-        <v>-4198</v>
+        <v>-2698</v>
       </c>
     </row>
     <row r="10">
@@ -16504,10 +16561,10 @@
         <v>16150</v>
       </c>
       <c r="E10" s="51" t="n">
-        <v>17865</v>
+        <v>14865</v>
       </c>
       <c r="F10" s="51" t="n">
-        <v>-1715</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="11">
@@ -16526,10 +16583,10 @@
         <v>25500</v>
       </c>
       <c r="E11" s="51" t="n">
-        <v>20730</v>
+        <v>17730</v>
       </c>
       <c r="F11" s="51" t="n">
-        <v>4770</v>
+        <v>7770</v>
       </c>
     </row>
     <row r="12">
@@ -16548,10 +16605,10 @@
         <v>34000</v>
       </c>
       <c r="E12" s="51" t="n">
-        <v>23040</v>
+        <v>20040</v>
       </c>
       <c r="F12" s="51" t="n">
-        <v>10960</v>
+        <v>13960</v>
       </c>
     </row>
     <row r="13">
@@ -16570,10 +16627,10 @@
         <v>42500</v>
       </c>
       <c r="E13" s="51" t="n">
-        <v>25350</v>
+        <v>22350</v>
       </c>
       <c r="F13" s="51" t="n">
-        <v>17150</v>
+        <v>20150</v>
       </c>
     </row>
     <row r="14">
@@ -16592,10 +16649,10 @@
         <v>6800</v>
       </c>
       <c r="E14" s="53" t="n">
-        <v>10980</v>
+        <v>9480</v>
       </c>
       <c r="F14" s="53" t="n">
-        <v>-4180</v>
+        <v>-2680</v>
       </c>
     </row>
     <row r="15">
@@ -16614,10 +16671,10 @@
         <v>23800</v>
       </c>
       <c r="E15" s="53" t="n">
-        <v>22656</v>
+        <v>19656</v>
       </c>
       <c r="F15" s="53" t="n">
-        <v>1144</v>
+        <v>4144</v>
       </c>
     </row>
     <row r="16">
@@ -16636,10 +16693,10 @@
         <v>37400</v>
       </c>
       <c r="E16" s="53" t="n">
-        <v>28176</v>
+        <v>25176</v>
       </c>
       <c r="F16" s="53" t="n">
-        <v>9224</v>
+        <v>12224</v>
       </c>
     </row>
     <row r="17">
@@ -16658,10 +16715,10 @@
         <v>51000</v>
       </c>
       <c r="E17" s="53" t="n">
-        <v>32856</v>
+        <v>29856</v>
       </c>
       <c r="F17" s="53" t="n">
-        <v>18144</v>
+        <v>21144</v>
       </c>
     </row>
     <row r="18">
@@ -16680,10 +16737,10 @@
         <v>64600</v>
       </c>
       <c r="E18" s="53" t="n">
-        <v>37536</v>
+        <v>34536</v>
       </c>
       <c r="F18" s="53" t="n">
-        <v>27064</v>
+        <v>30064</v>
       </c>
     </row>
     <row r="19">
@@ -16804,25 +16861,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="49" t="n">
-        <v>16000</v>
+        <v>13999.98</v>
       </c>
       <c r="C5" s="49" t="n">
-        <v>2720</v>
+        <v>2380</v>
       </c>
       <c r="D5" s="49" t="n">
-        <v>7032.01</v>
+        <v>7097.99</v>
       </c>
       <c r="E5" s="49" t="n">
-        <v>-4312.01</v>
+        <v>-4717.99</v>
       </c>
       <c r="F5" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="49" t="n">
-        <v>-4312.01</v>
+        <v>-4717.99</v>
       </c>
       <c r="H5" s="57" t="n">
-        <v>-1.585297794117647</v>
+        <v>-1.982348739495798</v>
       </c>
     </row>
     <row r="6">
@@ -16830,25 +16887,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="49" t="n">
-        <v>55000.01</v>
+        <v>48000.01</v>
       </c>
       <c r="C6" s="49" t="n">
-        <v>9350.01</v>
+        <v>8160.01</v>
       </c>
       <c r="D6" s="49" t="n">
-        <v>15128.99</v>
+        <v>16032</v>
       </c>
       <c r="E6" s="49" t="n">
-        <v>-5778.98</v>
+        <v>-7871.99</v>
       </c>
       <c r="F6" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="49" t="n">
-        <v>-5778.98</v>
+        <v>-7871.99</v>
       </c>
       <c r="H6" s="57" t="n">
-        <v>-0.618072066233084</v>
+        <v>-0.9647034746280948</v>
       </c>
     </row>
     <row r="7">
@@ -16856,25 +16913,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="49" t="n">
-        <v>90000</v>
+        <v>74999.98</v>
       </c>
       <c r="C7" s="49" t="n">
-        <v>15300</v>
+        <v>12750.02</v>
       </c>
       <c r="D7" s="49" t="n">
-        <v>17034.01</v>
+        <v>17492.99</v>
       </c>
       <c r="E7" s="49" t="n">
-        <v>-1734.01</v>
+        <v>-4742.97</v>
       </c>
       <c r="F7" s="49" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="49" t="n">
-        <v>-1734.01</v>
+        <v>-4742.97</v>
       </c>
       <c r="H7" s="57" t="n">
-        <v>-0.1133339869281048</v>
+        <v>-0.3719970635340182</v>
       </c>
     </row>
     <row r="8" ht="39.95" customHeight="1" s="32">
@@ -16882,25 +16939,25 @@
         <v>4</v>
       </c>
       <c r="B8" s="58" t="n">
-        <v>120000.01</v>
+        <v>100000.01</v>
       </c>
       <c r="C8" s="49" t="n">
-        <v>20400.01</v>
+        <v>17000.01</v>
       </c>
       <c r="D8" s="49" t="n">
-        <v>18024.01</v>
+        <v>18432</v>
       </c>
       <c r="E8" s="49" t="n">
-        <v>2376</v>
+        <v>-1431.99</v>
       </c>
       <c r="F8" s="49" t="n">
-        <v>356.4</v>
+        <v>0</v>
       </c>
       <c r="G8" s="49" t="n">
-        <v>2019.6</v>
+        <v>-1431.99</v>
       </c>
       <c r="H8" s="57" t="n">
-        <v>0.09899995147061189</v>
+        <v>-0.08423465633255499</v>
       </c>
     </row>
     <row r="9">
@@ -16908,25 +16965,25 @@
         <v>5</v>
       </c>
       <c r="B9" s="49" t="n">
-        <v>145000.01</v>
+        <v>124999.98</v>
       </c>
       <c r="C9" s="49" t="n">
-        <v>24650</v>
+        <v>21249.99</v>
       </c>
       <c r="D9" s="49" t="n">
-        <v>18819.01</v>
+        <v>18686.99</v>
       </c>
       <c r="E9" s="49" t="n">
-        <v>5830.99</v>
+        <v>2563</v>
       </c>
       <c r="F9" s="49" t="n">
-        <v>874.65</v>
+        <v>384.45</v>
       </c>
       <c r="G9" s="49" t="n">
-        <v>4956.34</v>
+        <v>2178.55</v>
       </c>
       <c r="H9" s="57" t="n">
-        <v>0.2010686206896552</v>
+        <v>0.1025200482447286</v>
       </c>
     </row>
     <row r="10"/>
@@ -16991,19 +17048,19 @@
         <v>4760.01</v>
       </c>
       <c r="D14" s="51" t="n">
-        <v>8958.01</v>
+        <v>7458.01</v>
       </c>
       <c r="E14" s="51" t="n">
-        <v>-4198</v>
+        <v>-2698</v>
       </c>
       <c r="F14" s="51" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="51" t="n">
-        <v>-4198</v>
+        <v>-2698</v>
       </c>
       <c r="H14" s="60" t="n">
-        <v>-0.8819309203131922</v>
+        <v>-0.5668055319211512</v>
       </c>
     </row>
     <row r="15">
@@ -17017,19 +17074,19 @@
         <v>16150</v>
       </c>
       <c r="D15" s="51" t="n">
-        <v>17864.98</v>
+        <v>14864.98</v>
       </c>
       <c r="E15" s="51" t="n">
-        <v>-1714.98</v>
+        <v>1285.02</v>
       </c>
       <c r="F15" s="51" t="n">
-        <v>0</v>
+        <v>192.75</v>
       </c>
       <c r="G15" s="51" t="n">
-        <v>-1714.98</v>
+        <v>1092.27</v>
       </c>
       <c r="H15" s="60" t="n">
-        <v>-0.1061907120743034</v>
+        <v>0.06763263157894721</v>
       </c>
     </row>
     <row r="16">
@@ -17043,19 +17100,19 @@
         <v>25500</v>
       </c>
       <c r="D16" s="51" t="n">
-        <v>20730</v>
+        <v>17730</v>
       </c>
       <c r="E16" s="51" t="n">
-        <v>4770</v>
+        <v>7770</v>
       </c>
       <c r="F16" s="51" t="n">
-        <v>715.5</v>
+        <v>1165.5</v>
       </c>
       <c r="G16" s="51" t="n">
-        <v>4054.5</v>
+        <v>6604.5</v>
       </c>
       <c r="H16" s="60" t="n">
-        <v>0.1590000000000001</v>
+        <v>0.2590000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -17069,19 +17126,19 @@
         <v>33999.99</v>
       </c>
       <c r="D17" s="51" t="n">
-        <v>23039.98</v>
+        <v>20039.98</v>
       </c>
       <c r="E17" s="51" t="n">
-        <v>10960.01</v>
+        <v>13960.01</v>
       </c>
       <c r="F17" s="51" t="n">
-        <v>1644</v>
+        <v>2094</v>
       </c>
       <c r="G17" s="51" t="n">
-        <v>9316.01</v>
+        <v>11866.01</v>
       </c>
       <c r="H17" s="60" t="n">
-        <v>0.2740003305883325</v>
+        <v>0.3490003526471624</v>
       </c>
     </row>
     <row r="18">
@@ -17095,19 +17152,19 @@
         <v>42500.01</v>
       </c>
       <c r="D18" s="51" t="n">
-        <v>25350</v>
+        <v>22350</v>
       </c>
       <c r="E18" s="51" t="n">
-        <v>17150.01</v>
+        <v>20150.01</v>
       </c>
       <c r="F18" s="51" t="n">
-        <v>2572.5</v>
+        <v>3022.5</v>
       </c>
       <c r="G18" s="51" t="n">
-        <v>14577.51</v>
+        <v>17127.51</v>
       </c>
       <c r="H18" s="60" t="n">
-        <v>0.3430001192940895</v>
+        <v>0.4030001051764458</v>
       </c>
     </row>
     <row r="19"/>
@@ -17172,19 +17229,19 @@
         <v>6799.99</v>
       </c>
       <c r="D23" s="53" t="n">
-        <v>10979.99</v>
+        <v>9479.99</v>
       </c>
       <c r="E23" s="53" t="n">
-        <v>-4180</v>
+        <v>-2680</v>
       </c>
       <c r="F23" s="53" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="53" t="n">
-        <v>-4180</v>
+        <v>-2680</v>
       </c>
       <c r="H23" s="62" t="n">
-        <v>-0.6147067863335096</v>
+        <v>-0.3941182266444512</v>
       </c>
     </row>
     <row r="24">
@@ -17198,19 +17255,19 @@
         <v>23799.99</v>
       </c>
       <c r="D24" s="53" t="n">
-        <v>22656.01</v>
+        <v>19656.01</v>
       </c>
       <c r="E24" s="53" t="n">
-        <v>1143.98</v>
+        <v>4143.98</v>
       </c>
       <c r="F24" s="53" t="n">
-        <v>171.6</v>
+        <v>621.6</v>
       </c>
       <c r="G24" s="53" t="n">
-        <v>972.38</v>
+        <v>3522.38</v>
       </c>
       <c r="H24" s="62" t="n">
-        <v>0.04085644573800253</v>
+        <v>0.1479993478988858</v>
       </c>
     </row>
     <row r="25">
@@ -17224,19 +17281,19 @@
         <v>37399.99</v>
       </c>
       <c r="D25" s="53" t="n">
-        <v>28176.01</v>
+        <v>25176.01</v>
       </c>
       <c r="E25" s="53" t="n">
-        <v>9223.98</v>
+        <v>12223.98</v>
       </c>
       <c r="F25" s="53" t="n">
-        <v>1383.6</v>
+        <v>1833.6</v>
       </c>
       <c r="G25" s="53" t="n">
-        <v>7840.38</v>
+        <v>10390.38</v>
       </c>
       <c r="H25" s="62" t="n">
-        <v>0.2096359651433061</v>
+        <v>0.2778178015555618</v>
       </c>
     </row>
     <row r="26">
@@ -17250,19 +17307,19 @@
         <v>50999.99</v>
       </c>
       <c r="D26" s="53" t="n">
-        <v>32856.01</v>
+        <v>29856.01</v>
       </c>
       <c r="E26" s="53" t="n">
-        <v>18143.98</v>
+        <v>21143.98</v>
       </c>
       <c r="F26" s="53" t="n">
-        <v>2721.6</v>
+        <v>3171.6</v>
       </c>
       <c r="G26" s="53" t="n">
-        <v>15422.38</v>
+        <v>17972.38</v>
       </c>
       <c r="H26" s="62" t="n">
-        <v>0.3023997259607306</v>
+        <v>0.3523997357646541</v>
       </c>
     </row>
     <row r="27">
@@ -17276,19 +17333,19 @@
         <v>64599.99</v>
       </c>
       <c r="D27" s="53" t="n">
-        <v>37536.02</v>
+        <v>34536.02</v>
       </c>
       <c r="E27" s="53" t="n">
-        <v>27063.97</v>
+        <v>30063.97</v>
       </c>
       <c r="F27" s="53" t="n">
-        <v>4059.6</v>
+        <v>4509.6</v>
       </c>
       <c r="G27" s="53" t="n">
-        <v>23004.37</v>
+        <v>25554.37</v>
       </c>
       <c r="H27" s="62" t="n">
-        <v>0.3561049235456539</v>
+        <v>0.3955786138666586</v>
       </c>
     </row>
     <row r="28"/>
